--- a/nola_knowledge_base.xlsx
+++ b/nola_knowledge_base.xlsx
@@ -7,11 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nola" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Base de Conhecimento" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legenda" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nola'!$A$1:$D$20</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,10 +39,27 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00111827"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00111827"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="006B7280"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -52,56 +68,87 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FD6263"/>
-        <bgColor rgb="00FD6263"/>
+        <fgColor rgb="00111827"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EBF8FF"/>
-        <bgColor rgb="00EBF8FF"/>
+        <fgColor rgb="00FCE9E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0FFF4"/>
-        <bgColor rgb="00F0FFF4"/>
+        <fgColor rgb="00ECFDF5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFF0"/>
-        <bgColor rgb="00FFFFF0"/>
+        <fgColor rgb="00EFF6FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF0F6"/>
-        <bgColor rgb="00FFF0F6"/>
+        <fgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5F0FF"/>
-        <bgColor rgb="00F5F0FF"/>
+        <fgColor rgb="00F5F3FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF8F0"/>
-        <bgColor rgb="00FFF8F0"/>
+        <fgColor rgb="00FFF7ED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0FDFA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0FDF4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF2FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDF4FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEFCE8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF7F7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F0F9FF"/>
-        <bgColor rgb="00F0F9FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF5F5"/>
-        <bgColor rgb="00FFF5F5"/>
+        <fgColor rgb="00FFF9F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -115,74 +162,317 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00E2E8F0"/>
+        <color rgb="00D1D5DB"/>
       </left>
       <right style="thin">
-        <color rgb="00E2E8F0"/>
+        <color rgb="00D1D5DB"/>
       </right>
       <top style="thin">
-        <color rgb="00E2E8F0"/>
+        <color rgb="00D1D5DB"/>
       </top>
       <bottom style="thin">
-        <color rgb="00E2E8F0"/>
+        <color rgb="00D1D5DB"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -549,457 +839,2334 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:E83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>pergunta</t>
-        </is>
-      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>resposta</t>
+          <t>Pergunta</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>tags</t>
+          <t>Resposta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Tags</t>
         </is>
       </c>
     </row>
     <row r="2" ht="60" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>geral</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>O que é o Nola?</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>O Nola é um ecossistema completo de gestão para restaurantes que integra PDV, financeiro, estoque, equipe e inteligência em uma única plataforma. Foi criado por donos de restaurante para donos de restaurante.</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>nola, sistema, o que é</t>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>O Nola é um ecossistema completo de gestão para food service. Integra PDV, financeiro, estoque, equipe e inteligência em uma única plataforma, criada por donos de restaurante para donos de restaurante.</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>nola, o que é, sistema, plataforma, gestão</t>
         </is>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>geral</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Qual o diferencial do Nola?</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>O diferencial do Nola é integrar tudo em um único sistema: PDV, financeiro com DRE automático, estoque com CMV real, gestão de equipe com gamificação e alertas inteligentes no WhatsApp. Sem precisar de vários sistemas que não conversam entre si.</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>diferencial, vantagem</t>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Qual é o diferencial do Nola?</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>O Nola nasceu dentro de um restaurante, não em um laboratório de tecnologia. Cada funcionalidade foi criada para resolver uma dor real do dia a dia. Além disso, integra todos os módulos: os dados de vendas alimentam o financeiro, o estoque e os alertas automaticamente.</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>diferencial, vantagem, por que escolher</t>
         </is>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>geral</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Para quem é o Nola?</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>O Nola atende restaurantes de todos os portes: do pequeno restaurante de bairro a redes com dezenas de unidades. Serve para pizzarias, hamburguerias, cafeterias, bistrôs, dark kitchens, franquias e qualquer negócio de food service.</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>para quem, público, segmento, tipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>geral</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>O Nola é 100% online?</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Sim, o Nola é 100% em nuvem. Você acessa de qualquer dispositivo com internet — computador, tablet ou celular. O PDV também tem modo offline para não parar na queda de internet, sincronizando tudo automaticamente quando a conexão voltar.</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>online, nuvem, cloud, offline, internet</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>geral</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Quantos restaurantes usam o Nola?</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>O Nola atende mais de 500 restaurantes em todo o Brasil, gerenciando mais de R$ 26 milhões por mês e processando mais de 340 mil pedidos por dia.</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>clientes, restaurantes atendidos, números, tamanho</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>geral</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>O Nola substitui vários sistemas?</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Sim! O Nola substitui PDV, sistema financeiro, controle de estoque, gestão de equipe e BI separados. Em vez de 3, 4 sistemas que não conversam entre si, você tem um único ecossistema integrado.</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>substituir, sistemas, integração, unificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>geral</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Como o Nola ajuda a reduzir custos?</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>O Nola reduz custos ao eliminar sistemas duplicados, mostrar o CMV real (não no achismo), detectar desvios de estoque, automatizar o financeiro (sem planilheiro) e recuperar tributos pagos a maior via BPO Tributário.</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>custos, redução, economia, ROI</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>geral</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>E se eu já uso outro sistema?</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Nossa equipe de CS cuida da migração com importação de cardápio, histórico e configurações. O processo é feito com suporte dedicado para não impactar a operação. Você não fica sozinho na troca.</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>migração, trocar, outro sistema, transição</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>planos</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Qual o preço do Nola?</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Os planos do Nola começam a partir de R$ 450/mês com gestão completa. Para conhecer o plano ideal para o seu negócio, recomendo agendar uma demonstração gratuita com nossa equipe.</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>preço, plano, valor, custo</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Quais são os planos disponíveis?</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>O Nola tem 4 planos: Essencial (faturamento até R$40k/mês), Profissional (R$40k–150k/mês), Premium (R$150k–300k/mês) e Enterprise (R$300k+ ou 3+ unidades). Todos começam com 30 dias grátis.</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>planos, opções, preço, valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>planos</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>O Nola tem plano gratuito?</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>O Nola não tem plano gratuito, mas oferece uma demonstração 100% gratuita e sem compromisso para você conhecer o sistema antes de contratar.</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>gratuito, free, teste</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>O que inclui o plano Essencial?</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>PDV completo (mesa, balcão, delivery), integração com iFood e Rappi, fechamento de caixa diário, contas a pagar/receber, importação automática de NF, relatórios essenciais, 1 admin + 3 operadores e suporte via chat em horário comercial.</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>essencial, plano básico, entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>planos</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>O que inclui o plano Profissional?</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Tudo do Essencial mais: DRE automatizado completo, conciliação bancária automática, fluxo de caixa com previsão, estoque + fichas técnicas, CMV real vs. teórico, contagem por áudio, cardápio avançado, metas inteligentes, KDS incluso, alertas WhatsApp (1 número), 3 admins + operadores ilimitados, suporte seg-sáb 8h-22h.</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>profissional, plano intermediário, core</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>planos</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>O que inclui o plano Premium?</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Tudo do Profissional mais: Clara IA (assistente via WhatsApp), CRM + Fidelidade, Cardápio Digital Interativo, Guia de Gente completo (RH), Rotinas e Tarefas, Nola Educa (plataforma de aprendizagem), multi-marca (1 extra inclusa), alertas WhatsApp (3 números), admins ilimitados, suporte 7 dias 8h-23h, implantação assistida com especialista.</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>premium, plano completo, ecossistema</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>planos</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>O que inclui o plano Enterprise?</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Tudo do Premium mais: dashboard consolidado multi-loja, marcas ilimitadas, API customizada, desconto progressivo por volume, gerente de conta dedicado, SLA de suporte garantido, implantação white-glove, acesso antecipado a novos módulos. Para redes de 3+ unidades ou faturamento acima de R$300k/mês.</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>enterprise, rede, multi-loja, grande porte</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>planos</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Qual o preço de cada plano?</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Os planos começam a partir de R$450/mês (Essencial). Para valores exatos dos planos Profissional, Premium e Enterprise, o ideal é agendar uma demonstração — nossa equipe monta a proposta certa para o seu porte. Todos os planos começam com 30 dias grátis.</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>preço, valor, custo, mensalidade, quanto custa</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>planos</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Tem período de teste gratuito?</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Sim! Todos os planos incluem 30 dias grátis. A implantação é instantânea — ao criar sua conta, o ambiente já sai pronto e personalizado para uso. Sem compromisso, sem cartão de crédito.</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>grátis, teste, trial, free, 30 dias</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>planos</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Posso cancelar quando quiser?</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Sim, você pode cancelar quando quiser. Não há fidelidade obrigatória nos planos base. O Nola acredita que você fica porque quer resultado, não por contrato.</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>cancelar, fidelidade, contrato, permanência</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>planos</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Existe add-ons além dos planos?</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Sim! É possível adicionar: Clara IA, CRM + Fidelidade, marca adicional, alertas WhatsApp extras, Totem de Autoatendimento, Tablet de Mesa, SmartPOS, TEF, Balança Autoatendimento, serviços Supfy (marketplace), BPO Financeiro (+Controle), BPO Tributário (Recupera) e Consultoria Setup 1:1.</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>add-ons, extras, adicionais, periféricos</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>planos</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Qual plano é mais popular?</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>O plano Profissional é o mais popular — é indicado para restaurantes com faturamento entre R$40k e R$150k/mês e cobre gestão completa: PDV, financeiro com DRE, estoque, CMV real e suporte de segunda a sábado.</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>popular, recomendado, mais vendido</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>implementação</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>Quanto tempo leva para implementar o Nola?</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>A implementação do Nola leva em média 7 dias úteis. Nossa equipe de Customer Success acompanha todo o processo de onboarding com suporte dedicado.</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>implementação, tempo, prazo, instalar</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>A implantação é instantânea para a criação do ambiente. O onboarding completo (configuração de cardápio, treinamento da equipe, integrações) leva em média 7 dias úteis com suporte dedicado do time de CS.</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="inlineStr">
+        <is>
+          <t>implementação, tempo, prazo, instalar, setup</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>implementação</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>Como é feito o onboarding?</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>O onboarding é feito com apoio da nossa equipe de CS. Inclui configuração do sistema, cadastro de cardápio, treinamento da equipe e integração com seus canais de delivery.</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>onboarding, configuração, início</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>O onboarding inclui configuração completa do sistema, cadastro do cardápio, treinamento da equipe, integração com delivery e acompanhamento da primeira semana de operação. O plano Premium tem implantação assistida com especialista.</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="inlineStr">
+        <is>
+          <t>onboarding, configuração, início, treinamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>implementação</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>Precisa de equipamento especial para usar o Nola?</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>O Nola funciona em qualquer computador, tablet ou celular com internet. Para otimizar a operação, a Nola oferece hardware complementar vendido à parte: Totem de Autoatendimento, Tablet de Mesa, SmartPOS (maquininha integrada) e TEF.</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>equipamento, hardware, dispositivo, computador, tablet</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>implementação</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>O PDV funciona sem internet?</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>Sim! O PDV tem modo offline. Em caso de queda de internet, você continua operando normalmente. Quando a conexão for restabelecida, tudo é sincronizado automaticamente.</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>offline, sem internet, queda, funciona sem conexão</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>implementação</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>Posso usar em mais de um dispositivo ao mesmo tempo?</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>Sim, o Nola é multi-dispositivo. Você pode ter o PDV no balcão, o KDS na cozinha e o painel gerencial no seu celular simultaneamente, tudo sincronizado em tempo real.</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="inlineStr">
+        <is>
+          <t>multi-dispositivo, vários, simultâneo</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
         <is>
           <t>integração</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>O Nola integra com iFood e Rappi?</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Sim! O Nola integra 100% com iFood, Rappi e outros apps de delivery. Todos os pedidos de todos os canais aparecem em uma única tela, com KDS por praça para organizar a cozinha.</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>ifood, rappi, delivery, integração</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="C25" s="19" t="inlineStr">
+        <is>
+          <t>O Nola integra com iFood?</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>Sim! O Nola tem integração nativa com iFood. Todos os pedidos do iFood aparecem automaticamente na tela do PDV, sem precisar ficar na maquininha do iFood. O KDS da cozinha também recebe esses pedidos.</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>ifood, delivery, integração</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
         <is>
           <t>integração</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Quais integrações o Nola tem?</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>O Nola integra com iFood, Rappi, sistemas de pagamento, softwares de contabilidade e muito mais. Todos os dados centralizados em um único painel.</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>integração, sistema, parceiros</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>funcionalidades</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="C26" s="19" t="inlineStr">
+        <is>
+          <t>O Nola integra com Rappi?</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>Sim! O Nola integra com Rappi. Pedidos do Rappi entram automaticamente no PDV junto com os outros canais — balcão, mesas e outros apps — em uma tela unificada.</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>rappi, delivery, integração</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>integração</t>
+        </is>
+      </c>
+      <c r="C27" s="19" t="inlineStr">
+        <is>
+          <t>Quais apps de delivery o Nola integra?</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>O Nola integra com iFood, Rappi e Delivery Direto. Todos os pedidos de todos os canais aparecem em uma única tela, com roteamento automático para o KDS da cozinha.</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>delivery, apps, integração, marketplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>integração</t>
+        </is>
+      </c>
+      <c r="C28" s="19" t="inlineStr">
+        <is>
+          <t>O Nola integra com sistemas de pagamento?</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>Sim! O Nola integra via TEF com as principais maquininhas do mercado. O SmartPOS é a solução própria integrada ao PDV. Também faz conciliação automática dos recebíveis via OFX.</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>pagamento, maquininha, tef, smartpos, cartão</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>integração</t>
+        </is>
+      </c>
+      <c r="C29" s="19" t="inlineStr">
+        <is>
+          <t>O Nola integra com contabilidade?</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>Sim! O módulo financeiro faz conciliação bancária via OFX e importação automática de notas fiscais (NF-e). O BPO Tributário (Recupera) também trabalha integrado aos dados reais do Nola.</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>contabilidade, nfe, nota fiscal, ofx, conciliação</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>integração</t>
+        </is>
+      </c>
+      <c r="C30" s="19" t="inlineStr">
+        <is>
+          <t>O Nola tem API aberta?</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>Sim, API customizada está disponível no plano Enterprise. Para integrações específicas com ERPs, sistemas de gestão ou plataformas proprietárias, é possível via esse plano.</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>api, integração, erp, customizado</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>pdv_operacao</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
         <is>
           <t>Como funciona o PDV do Nola?</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>O PDV do Nola é 100% em nuvem e não cai na hora do pico. Gerencia mesas, balcão, delivery e tem painel KDS para a cozinha. Interface intuitiva que funciona em tablet ou computador.</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>pdv, caixa, frente de caixa</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>funcionalidades</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="D31" s="25" t="inlineStr">
+        <is>
+          <t>O PDV do Nola é 100% em nuvem, não cai na hora do pico e gerencia mesa, balcão, delivery e QR Code em uma tela só. Tem KDS (painel de cozinha) integrado por praça, acessível em qualquer dispositivo.</t>
+        </is>
+      </c>
+      <c r="E31" s="26" t="inlineStr">
+        <is>
+          <t>pdv, frente de caixa, caixa, operação</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" s="22" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>pdv_operacao</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>O que é o KDS?</t>
+        </is>
+      </c>
+      <c r="D32" s="25" t="inlineStr">
+        <is>
+          <t>KDS (Kitchen Display System) é o painel digital da cozinha. Substitui os papéis de pedido, mostrando para cada praça (grelha, fritadeira, montagem) apenas os pedidos que precisa preparar, com status em tempo real.</t>
+        </is>
+      </c>
+      <c r="E32" s="26" t="inlineStr">
+        <is>
+          <t>kds, cozinha, painel, display</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="22" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>pdv_operacao</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>Como funciona a gestão de mesas?</t>
+        </is>
+      </c>
+      <c r="D33" s="25" t="inlineStr">
+        <is>
+          <t>O Nola tem gestão de mesas com mapa visual do salão, abertura e fechamento de comanda, transferência de itens entre mesas e divisão de conta. Tudo em tempo real, acessível pelo tablet do garçom ou pelo computador do caixa.</t>
+        </is>
+      </c>
+      <c r="E33" s="26" t="inlineStr">
+        <is>
+          <t>mesas, salão, comanda, garçom</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="22" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>pdv_operacao</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>O Nola tem cardápio digital?</t>
+        </is>
+      </c>
+      <c r="D34" s="25" t="inlineStr">
+        <is>
+          <t>Sim! O Cardápio Digital Interativo está disponível no plano Premium. Clientes acessam via QR Code na mesa, fazem o pedido e ele entra direto no PDV e no KDS.</t>
+        </is>
+      </c>
+      <c r="E34" s="26" t="inlineStr">
+        <is>
+          <t>cardápio digital, qr code, self-service, autoatendimento</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="22" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>pdv_operacao</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>O Nola tem totem de autoatendimento?</t>
+        </is>
+      </c>
+      <c r="D35" s="25" t="inlineStr">
+        <is>
+          <t>Sim! O Totem de Autoatendimento é um hardware disponível para compra separada, compatível com os planos Profissional e superiores. Reduz fila, aumenta ticket médio e libera a equipe para o atendimento.</t>
+        </is>
+      </c>
+      <c r="E35" s="26" t="inlineStr">
+        <is>
+          <t>totem, autoatendimento, self-checkout, kiosk</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="22" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="23" t="inlineStr">
+        <is>
+          <t>pdv_operacao</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>O Nola tem controle de caixa?</t>
+        </is>
+      </c>
+      <c r="D36" s="25" t="inlineStr">
+        <is>
+          <t>Sim! O PDV tem abertura e fechamento de caixa diário com conferência de sangrias, suprimentos e formas de pagamento. Os dados alimentam automaticamente o módulo financeiro.</t>
+        </is>
+      </c>
+      <c r="E36" s="26" t="inlineStr">
+        <is>
+          <t>caixa, fechamento, abertura, sangria, conferência</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="27" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="28" t="inlineStr">
+        <is>
+          <t>financeiro</t>
+        </is>
+      </c>
+      <c r="C37" s="29" t="inlineStr">
         <is>
           <t>Como funciona o módulo financeiro?</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>O módulo financeiro gera DRE confiável automaticamente, controla fluxo de caixa em tempo real e faz conciliação via OFX. Sem planilha, sem retrabalho. Você vê a saúde financeira do restaurante em tempo real.</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>financeiro, dre, fluxo de caixa</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>funcionalidades</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="D37" s="30" t="inlineStr">
+        <is>
+          <t>O módulo financeiro gera DRE automático a partir das vendas e despesas reais, controla fluxo de caixa em tempo real, faz conciliação bancária via OFX e gerencia contas a pagar e receber. Sem planilha, sem retrabalho.</t>
+        </is>
+      </c>
+      <c r="E37" s="31" t="inlineStr">
+        <is>
+          <t>financeiro, dre, fluxo de caixa, contas</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="27" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="28" t="inlineStr">
+        <is>
+          <t>financeiro</t>
+        </is>
+      </c>
+      <c r="C38" s="29" t="inlineStr">
+        <is>
+          <t>O que é o DRE automático do Nola?</t>
+        </is>
+      </c>
+      <c r="D38" s="30" t="inlineStr">
+        <is>
+          <t>O DRE (Demonstração do Resultado do Exercício) do Nola é gerado automaticamente todo mês com base nas vendas, custos e despesas reais cadastrados. Mostra exatamente onde você está ganhando e onde pode melhorar, sem precisar de contador para montar.</t>
+        </is>
+      </c>
+      <c r="E38" s="31" t="inlineStr">
+        <is>
+          <t>dre, resultado, relatório financeiro, automático</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" s="27" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="28" t="inlineStr">
+        <is>
+          <t>financeiro</t>
+        </is>
+      </c>
+      <c r="C39" s="29" t="inlineStr">
+        <is>
+          <t>O que é o +Controle (BPO Financeiro)?</t>
+        </is>
+      </c>
+      <c r="D39" s="30" t="inlineStr">
+        <is>
+          <t>O +Controle é o serviço de BPO Financeiro da Nola: uma equipe especializada que cuida de contas a pagar, contas a receber, conciliação bancária, fluxo de caixa e DRE mensal por você. Disponível nos planos Profissional e superiores (add-on).</t>
+        </is>
+      </c>
+      <c r="E39" s="31" t="inlineStr">
+        <is>
+          <t>bpo financeiro, +controle, terceirizar financeiro, gestão financeira</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" s="27" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="28" t="inlineStr">
+        <is>
+          <t>financeiro</t>
+        </is>
+      </c>
+      <c r="C40" s="29" t="inlineStr">
+        <is>
+          <t>O +Controle tem dois planos?</t>
+        </is>
+      </c>
+      <c r="D40" s="30" t="inlineStr">
+        <is>
+          <t>Sim! Plano Essencial (sem inclusão de pagamentos) cobre contas a pagar, contas a receber, conciliação, fluxo de caixa e DRE. Plano Completo inclui tudo isso + inclusão de pagamentos no banco.</t>
+        </is>
+      </c>
+      <c r="E40" s="31" t="inlineStr">
+        <is>
+          <t>mais controle, bpo, plano essencial, plano completo</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" s="27" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="28" t="inlineStr">
+        <is>
+          <t>financeiro</t>
+        </is>
+      </c>
+      <c r="C41" s="29" t="inlineStr">
+        <is>
+          <t>Como funciona a conciliação bancária?</t>
+        </is>
+      </c>
+      <c r="D41" s="30" t="inlineStr">
+        <is>
+          <t>O Nola importa o extrato bancário via arquivo OFX e faz a conciliação automática com as entradas e saídas registradas no sistema. Identifica divergências e gera relatórios de saldo conferido.</t>
+        </is>
+      </c>
+      <c r="E41" s="31" t="inlineStr">
+        <is>
+          <t>conciliação, banco, ofx, extrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" s="32" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="33" t="inlineStr">
+        <is>
+          <t>tributario</t>
+        </is>
+      </c>
+      <c r="C42" s="34" t="inlineStr">
+        <is>
+          <t>O que é o Recupera (BPO Tributário)?</t>
+        </is>
+      </c>
+      <c r="D42" s="35" t="inlineStr">
+        <is>
+          <t>O Recupera é o serviço de BPO Tributário especializado em food service da Nola. Identifica pagamentos indevidos de PIS/COFINS em produtos monofásicos, reclassifica NCMs incorretos e recupera créditos dos últimos 5 anos via PER/DCOMP, sem ação judicial.</t>
+        </is>
+      </c>
+      <c r="E42" s="36" t="inlineStr">
+        <is>
+          <t>tributário, recupera, imposto, pis, cofins, ncm</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" s="32" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="33" t="inlineStr">
+        <is>
+          <t>tributario</t>
+        </is>
+      </c>
+      <c r="C43" s="34" t="inlineStr">
+        <is>
+          <t>Quanto posso recuperar com o Recupera?</t>
+        </is>
+      </c>
+      <c r="D43" s="35" t="inlineStr">
+        <is>
+          <t>A economia média fica entre 3% a 8% na margem líquida. O diagnóstico inicial é gratuito: você envia os XMLs dos últimos 12 meses e recebemos um relatório com estimativa de créditos recuperáveis dos últimos 5 anos.</t>
+        </is>
+      </c>
+      <c r="E43" s="36" t="inlineStr">
+        <is>
+          <t>recuperação, crédito, imposto, valor, quanto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" s="32" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="33" t="inlineStr">
+        <is>
+          <t>tributario</t>
+        </is>
+      </c>
+      <c r="C44" s="34" t="inlineStr">
+        <is>
+          <t>Como funciona o processo do Recupera?</t>
+        </is>
+      </c>
+      <c r="D44" s="35" t="inlineStr">
+        <is>
+          <t>4 etapas: (1) Raio-X Tributário gratuito com XMLs de 12 meses; (2) Auditoria completa de NCM/CST/CFOP; (3) Produção jurídica com PER/DCOMP; (4) Acompanhamento de deferimentos e implementação de rotinas preventivas.</t>
+        </is>
+      </c>
+      <c r="E44" s="36" t="inlineStr">
+        <is>
+          <t>como funciona, etapas, processo, raio-x</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" s="32" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="33" t="inlineStr">
+        <is>
+          <t>tributario</t>
+        </is>
+      </c>
+      <c r="C45" s="34" t="inlineStr">
+        <is>
+          <t>O Recupera cobra honorários de êxito?</t>
+        </is>
+      </c>
+      <c r="D45" s="35" t="inlineStr">
+        <is>
+          <t>Sim! O modelo principal é de honorários de êxito — você paga apenas um percentual sobre o valor efetivamente recuperado. Só paga quando o dinheiro entra. Há também o BPO Preventivo com mensalidade para monitoramento contínuo.</t>
+        </is>
+      </c>
+      <c r="E45" s="36" t="inlineStr">
+        <is>
+          <t>honorários, êxito, cobrança, como cobra</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" s="32" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="33" t="inlineStr">
+        <is>
+          <t>tributario</t>
+        </is>
+      </c>
+      <c r="C46" s="34" t="inlineStr">
+        <is>
+          <t>O Recupera serve para qualquer restaurante?</t>
+        </is>
+      </c>
+      <c r="D46" s="35" t="inlineStr">
+        <is>
+          <t>Sim! O BPO Tributário está disponível para qualquer plano Nola. O diagnóstico gratuito (Raio-X) identifica se há oportunidade de recuperação antes de qualquer compromisso.</t>
+        </is>
+      </c>
+      <c r="E46" s="36" t="inlineStr">
+        <is>
+          <t>serve, qualquer, elegível, pré-requisito</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" s="37" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="38" t="inlineStr">
+        <is>
+          <t>estoque_compras</t>
+        </is>
+      </c>
+      <c r="C47" s="39" t="inlineStr">
         <is>
           <t>Como funciona o controle de estoque?</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>O estoque do Nola tem ficha técnica com baixa automática em cascata, contagem cega anti-fraude e CMV real (não no achismo). Você sabe exatamente quanto custa cada prato e onde está perdendo margem.</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>estoque, cmv, ficha técnica</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>funcionalidades</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>Como funciona a gestão de equipe?</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>O módulo de equipe tem onboarding digital, treinamentos com prova, checklists com foto, canal anônimo para funcionários e metas gamificadas. Padroniza a operação independente de quem está no turno.</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>equipe, funcionários, rh</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>funcionalidades</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>O que é o módulo de Inteligência?</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>O módulo de Inteligência do Nola tem alertas automáticos de cancelamentos, vendas suspeitas e desvios enviados direto no seu WhatsApp. É como ter um funcionário dedo-duro que monitora tudo 24h.</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>inteligência, alertas, relatórios, whatsapp</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>negócio</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>O Nola serve para meu tipo de restaurante?</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>O Nola atende restaurantes a la carte, pizzarias, hamburguerias, cafeterias, dark kitchens, bistrôs e franquias. Se você vende comida, o Nola foi feito para você.</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>tipo, restaurante, pizzaria, hamburgueria</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>negócio</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>O Nola atende franquias?</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
-        <is>
-          <t>Sim! O Nola tem módulo específico para franqueadoras com padronização multi-unidade, controle centralizado e relatórios consolidados de todas as unidades.</t>
-        </is>
-      </c>
-      <c r="D16" s="13" t="inlineStr">
-        <is>
-          <t>franquia, rede, multi-unidade</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="D47" s="40" t="inlineStr">
+        <is>
+          <t>O estoque tem ficha técnica com baixa automática em cascata (do insumo ao subproduto ao prato), contagem cega pelo celular (operador conta sem ver a posição do sistema, evitando fraude) e CMV real por produto em tempo real.</t>
+        </is>
+      </c>
+      <c r="E47" s="41" t="inlineStr">
+        <is>
+          <t>estoque, controle, baixa automática, insumos</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" s="37" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="38" t="inlineStr">
+        <is>
+          <t>estoque_compras</t>
+        </is>
+      </c>
+      <c r="C48" s="39" t="inlineStr">
+        <is>
+          <t>O que é o CMV e como o Nola ajuda?</t>
+        </is>
+      </c>
+      <c r="D48" s="40" t="inlineStr">
+        <is>
+          <t>CMV (Custo de Mercadoria Vendida) é o percentual do faturamento gasto com insumos. O Nola calcula o CMV real vs. teórico por produto, identifica desvios e gera alertas automáticos quando o CMV sai da meta.</t>
+        </is>
+      </c>
+      <c r="E48" s="41" t="inlineStr">
+        <is>
+          <t>cmv, custo, mercadoria, margem, food cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" s="37" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="38" t="inlineStr">
+        <is>
+          <t>estoque_compras</t>
+        </is>
+      </c>
+      <c r="C49" s="39" t="inlineStr">
+        <is>
+          <t>O que é ficha técnica com cascata?</t>
+        </is>
+      </c>
+      <c r="D49" s="40" t="inlineStr">
+        <is>
+          <t>A ficha técnica registra os ingredientes de cada prato com gramagem. A 'cascata' significa que quando você vende um prato, o estoque de todos os ingredientes é baixado automaticamente, inclusive sub-receitas (ex: o molho que leva tomate, azeite e alho).</t>
+        </is>
+      </c>
+      <c r="E49" s="41" t="inlineStr">
+        <is>
+          <t>ficha técnica, cascata, receita, ingredientes</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" s="37" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="38" t="inlineStr">
+        <is>
+          <t>estoque_compras</t>
+        </is>
+      </c>
+      <c r="C50" s="39" t="inlineStr">
+        <is>
+          <t>O que é o Supfy?</t>
+        </is>
+      </c>
+      <c r="D50" s="40" t="inlineStr">
+        <is>
+          <t>Supfy é o módulo de Compras &amp; Estoque integrado ao Nola. Inclui marketplace de cotação automatizada com fornecedores, controle de estoque em tempo real, ficha técnica precisa e alertas de CMV. Disponível como add-on a partir do plano Profissional.</t>
+        </is>
+      </c>
+      <c r="E50" s="41" t="inlineStr">
+        <is>
+          <t>supfy, compras, fornecedores, cotação, marketplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" s="37" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="38" t="inlineStr">
+        <is>
+          <t>estoque_compras</t>
+        </is>
+      </c>
+      <c r="C51" s="39" t="inlineStr">
+        <is>
+          <t>O Nola tem alertas de estoque mínimo?</t>
+        </is>
+      </c>
+      <c r="D51" s="40" t="inlineStr">
+        <is>
+          <t>Sim! Você define o estoque mínimo de cada insumo e recebe alertas automáticos quando está próximo do fim, via WhatsApp ou no painel de inteligência.</t>
+        </is>
+      </c>
+      <c r="E51" s="41" t="inlineStr">
+        <is>
+          <t>estoque mínimo, alerta, reposição</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" s="42" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="43" t="inlineStr">
+        <is>
+          <t>equipe</t>
+        </is>
+      </c>
+      <c r="C52" s="44" t="inlineStr">
+        <is>
+          <t>Como funciona o Guia de Gente?</t>
+        </is>
+      </c>
+      <c r="D52" s="45" t="inlineStr">
+        <is>
+          <t>O Guia de Gente é o módulo de gestão de equipe do Nola. Inclui: onboarding estruturado com trilha de treinamento, vídeos com prova (mínimo 80% de aprovação), checklists diários com foto obrigatória, canal anônimo de denúncias e metas gamificadas com ranking.</t>
+        </is>
+      </c>
+      <c r="E52" s="46" t="inlineStr">
+        <is>
+          <t>guia de gente, equipe, funcionários, rh, gege</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" s="42" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="43" t="inlineStr">
+        <is>
+          <t>equipe</t>
+        </is>
+      </c>
+      <c r="C53" s="44" t="inlineStr">
+        <is>
+          <t>O Nola tem plataforma de treinamento?</t>
+        </is>
+      </c>
+      <c r="D53" s="45" t="inlineStr">
+        <is>
+          <t>Sim! O Nola Educa é a plataforma de aprendizagem integrada, disponível no plano Premium. Permite criar trilhas de treinamento em vídeo, aplicar provas com nota mínima e acompanhar o progresso de cada funcionário.</t>
+        </is>
+      </c>
+      <c r="E53" s="46" t="inlineStr">
+        <is>
+          <t>treinamento, cursos, aprendizagem, nola educa</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" s="42" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="43" t="inlineStr">
+        <is>
+          <t>equipe</t>
+        </is>
+      </c>
+      <c r="C54" s="44" t="inlineStr">
+        <is>
+          <t>Como funcionam os checklists operacionais?</t>
+        </is>
+      </c>
+      <c r="D54" s="45" t="inlineStr">
+        <is>
+          <t>Os checklists do Nola permitem criar rotinas diárias com fotos obrigatórias como evidência. O gerente vê em tempo real quais tarefas foram concluídas e quais estão atrasadas, de qualquer dispositivo.</t>
+        </is>
+      </c>
+      <c r="E54" s="46" t="inlineStr">
+        <is>
+          <t>checklists, rotinas, tarefas, checklist, operacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" s="42" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="43" t="inlineStr">
+        <is>
+          <t>equipe</t>
+        </is>
+      </c>
+      <c r="C55" s="44" t="inlineStr">
+        <is>
+          <t>O Nola tem canal anônimo para funcionários?</t>
+        </is>
+      </c>
+      <c r="D55" s="45" t="inlineStr">
+        <is>
+          <t>Sim! O Guia de Gente inclui um canal anônimo onde funcionários podem reportar problemas, sugestões ou irregularidades sem se identificar. Isso ajuda a reduzir turnover e detectar fraudes internas.</t>
+        </is>
+      </c>
+      <c r="E55" s="46" t="inlineStr">
+        <is>
+          <t>canal anônimo, denúncia, feedback, funcionário</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" s="42" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="43" t="inlineStr">
+        <is>
+          <t>equipe</t>
+        </is>
+      </c>
+      <c r="C56" s="44" t="inlineStr">
+        <is>
+          <t>O Nola tem metas para equipe?</t>
+        </is>
+      </c>
+      <c r="D56" s="45" t="inlineStr">
+        <is>
+          <t>Sim! O módulo de equipe tem metas inteligentes baseadas em histórico de vendas, com ranking em tempo real no PDV. A gamificação motiva a equipe e cria competição saudável para bater metas.</t>
+        </is>
+      </c>
+      <c r="E56" s="46" t="inlineStr">
+        <is>
+          <t>metas, gamificação, ranking, performance, bonificação</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" s="47" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="48" t="inlineStr">
+        <is>
+          <t>inteligencia</t>
+        </is>
+      </c>
+      <c r="C57" s="49" t="inlineStr">
+        <is>
+          <t>Como funciona o módulo de Inteligência?</t>
+        </is>
+      </c>
+      <c r="D57" s="50" t="inlineStr">
+        <is>
+          <t>O módulo de Inteligência centraliza dados de todos os módulos (vendas, estoque, equipe, financeiro) e transforma em alertas automáticos no WhatsApp, dashboards em tempo real, relatórios comparativos por período e detecção de anomalias.</t>
+        </is>
+      </c>
+      <c r="E57" s="51" t="inlineStr">
+        <is>
+          <t>inteligência, alertas, relatórios, dashboard, bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" s="47" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="48" t="inlineStr">
+        <is>
+          <t>inteligencia</t>
+        </is>
+      </c>
+      <c r="C58" s="49" t="inlineStr">
+        <is>
+          <t>O que é o Funcionário Dedo-Duro?</t>
+        </is>
+      </c>
+      <c r="D58" s="50" t="inlineStr">
+        <is>
+          <t>É o sistema de alertas automáticos da Nola. Monitora cancelamentos suspeitos, desvios de CMV, vendas fora do padrão e outras anomalias, enviando alerta no WhatsApp do dono em tempo real. Você sabe o que está acontecendo na loja mesmo quando não está lá.</t>
+        </is>
+      </c>
+      <c r="E58" s="51" t="inlineStr">
+        <is>
+          <t>dedo-duro, alertas, whatsapp, monitoramento, fraude</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" s="47" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="48" t="inlineStr">
+        <is>
+          <t>inteligencia</t>
+        </is>
+      </c>
+      <c r="C59" s="49" t="inlineStr">
+        <is>
+          <t>O Nola envia resumo diário pelo WhatsApp?</t>
+        </is>
+      </c>
+      <c r="D59" s="50" t="inlineStr">
+        <is>
+          <t>Sim! O módulo de Inteligência envia resumos diários de vendas, CMV, ticket médio e comparativo com o período anterior direto no WhatsApp. Disponível a partir do plano Profissional (1 número) e expandido nos planos superiores.</t>
+        </is>
+      </c>
+      <c r="E59" s="51" t="inlineStr">
+        <is>
+          <t>whatsapp, resumo, diário, relatório, notificação</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" s="47" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="48" t="inlineStr">
+        <is>
+          <t>inteligencia</t>
+        </is>
+      </c>
+      <c r="C60" s="49" t="inlineStr">
+        <is>
+          <t>O que é a Clara IA?</t>
+        </is>
+      </c>
+      <c r="D60" s="50" t="inlineStr">
+        <is>
+          <t>Clara IA é a assistente estratégica da Nola por WhatsApp. Ela responde perguntas sobre o desempenho do restaurante, sugere ações baseadas nos dados e ajuda na tomada de decisão. Disponível no plano Premium e como add-on no Profissional.</t>
+        </is>
+      </c>
+      <c r="E60" s="51" t="inlineStr">
+        <is>
+          <t>clara ia, inteligência artificial, assistente, ia</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" s="47" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="48" t="inlineStr">
+        <is>
+          <t>inteligencia</t>
+        </is>
+      </c>
+      <c r="C61" s="49" t="inlineStr">
+        <is>
+          <t>O Nola tem dashboard em tempo real?</t>
+        </is>
+      </c>
+      <c r="D61" s="50" t="inlineStr">
+        <is>
+          <t>Sim! O painel de Inteligência mostra faturamento, CMV, ticket médio, pedidos e ranking de produtos em tempo real. Acessível no celular ou computador, com comparativo entre períodos e unidades.</t>
+        </is>
+      </c>
+      <c r="E61" s="51" t="inlineStr">
+        <is>
+          <t>dashboard, painel, tempo real, indicadores, kpi</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" s="52" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="53" t="inlineStr">
+        <is>
+          <t>franquias</t>
+        </is>
+      </c>
+      <c r="C62" s="54" t="inlineStr">
+        <is>
+          <t>O Nola serve para franqueadoras?</t>
+        </is>
+      </c>
+      <c r="D62" s="55" t="inlineStr">
+        <is>
+          <t>Sim! O Nola tem módulo específico para franqueadoras com dashboard consolidado de todas as unidades, ficha técnica padronizada, contagem cega anti-fraude, treinamento com prova, canal anônimo e ranking de performance entre lojas.</t>
+        </is>
+      </c>
+      <c r="E62" s="56" t="inlineStr">
+        <is>
+          <t>franquia, rede, multi-unidade, franqueadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" s="52" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="53" t="inlineStr">
+        <is>
+          <t>franquias</t>
+        </is>
+      </c>
+      <c r="C63" s="54" t="inlineStr">
+        <is>
+          <t>Como o Nola ajuda na padronização de franquias?</t>
+        </is>
+      </c>
+      <c r="D63" s="55" t="inlineStr">
+        <is>
+          <t>O Nola garante padronização via: ficha técnica única (com baixa automática em cascata igual em todas as unidades), trilha de treinamento obrigatória para novos funcionários, checklists operacionais com foto e comunicados centralizados pelo franqueador.</t>
+        </is>
+      </c>
+      <c r="E63" s="56" t="inlineStr">
+        <is>
+          <t>padronização, padrão, franquia, processos</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" s="52" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="53" t="inlineStr">
+        <is>
+          <t>franquias</t>
+        </is>
+      </c>
+      <c r="C64" s="54" t="inlineStr">
+        <is>
+          <t>Tem dashboard consolidado para redes?</t>
+        </is>
+      </c>
+      <c r="D64" s="55" t="inlineStr">
+        <is>
+          <t>Sim! No plano Enterprise, o franqueador tem visão executiva com KPIs de todas as unidades em tempo real: faturamento, CMV, ticket médio, margem e ranking de performance. Sem pedir relatório para ninguém.</t>
+        </is>
+      </c>
+      <c r="E64" s="56" t="inlineStr">
+        <is>
+          <t>consolidado, multi-loja, rede, visão geral</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" s="52" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="53" t="inlineStr">
+        <is>
+          <t>franquias</t>
+        </is>
+      </c>
+      <c r="C65" s="54" t="inlineStr">
+        <is>
+          <t>Quais redes já usam o Nola?</t>
+        </is>
+      </c>
+      <c r="D65" s="55" t="inlineStr">
+        <is>
+          <t>Entre as redes que usam o Nola estão: Jotajá, Love Chicken, Picanhas BBQ, Classudo, Vila Restaurante, Porks, Açougue Vegano e Brasa na Lenha, além de centenas de unidades individuais.</t>
+        </is>
+      </c>
+      <c r="E65" s="56" t="inlineStr">
+        <is>
+          <t>clientes, referências, quem usa, cases</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" s="57" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="58" t="inlineStr">
+        <is>
+          <t>tipos_negocio</t>
+        </is>
+      </c>
+      <c r="C66" s="59" t="inlineStr">
+        <is>
+          <t>O Nola funciona para pizzarias?</t>
+        </is>
+      </c>
+      <c r="D66" s="60" t="inlineStr">
+        <is>
+          <t>Sim! O Nola tem recursos específicos para pizzarias: gestão de meios a meio no cardápio, controle de ingredientes por tamanho, integração com delivery e KDS por praça (forno, montagem).</t>
+        </is>
+      </c>
+      <c r="E66" s="61" t="inlineStr">
+        <is>
+          <t>pizzaria, pizza, meios</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" s="57" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="58" t="inlineStr">
+        <is>
+          <t>tipos_negocio</t>
+        </is>
+      </c>
+      <c r="C67" s="59" t="inlineStr">
+        <is>
+          <t>O Nola funciona para hamburguerias?</t>
+        </is>
+      </c>
+      <c r="D67" s="60" t="inlineStr">
+        <is>
+          <t>Sim! Para hamburguerias o Nola integra todos os canais de delivery (iFood, Rappi), tem PDV rápido para pico de movimento, KDS de cozinha, controle de CMV por insumo e gestão de combos no cardápio.</t>
+        </is>
+      </c>
+      <c r="E67" s="61" t="inlineStr">
+        <is>
+          <t>hamburgueria, burguer, lanche</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" s="57" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="58" t="inlineStr">
+        <is>
+          <t>tipos_negocio</t>
+        </is>
+      </c>
+      <c r="C68" s="59" t="inlineStr">
+        <is>
+          <t>O Nola funciona para dark kitchens?</t>
+        </is>
+      </c>
+      <c r="D68" s="60" t="inlineStr">
+        <is>
+          <t>Sim! Para dark kitchens o Nola gerencia múltiplas marcas em uma única operação, centraliza todos os pedidos de delivery em uma tela e controla o CMV de cada marca separadamente.</t>
+        </is>
+      </c>
+      <c r="E68" s="61" t="inlineStr">
+        <is>
+          <t>dark kitchen, cozinha fantasma, multi-marca</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" s="57" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="58" t="inlineStr">
+        <is>
+          <t>tipos_negocio</t>
+        </is>
+      </c>
+      <c r="C69" s="59" t="inlineStr">
+        <is>
+          <t>O Nola funciona para cafeterias e bistrôs?</t>
+        </is>
+      </c>
+      <c r="D69" s="60" t="inlineStr">
+        <is>
+          <t>Sim! Para cafeterias e bistrôs o Nola otimiza o atendimento no balcão, controla estoque de ingredientes perecíveis, integra delivery quando aplicável e tem cardápio avançado com combos e subitens.</t>
+        </is>
+      </c>
+      <c r="E69" s="61" t="inlineStr">
+        <is>
+          <t>cafeteria, bistrô, café, lanchonete</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" s="57" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="58" t="inlineStr">
+        <is>
+          <t>tipos_negocio</t>
+        </is>
+      </c>
+      <c r="C70" s="59" t="inlineStr">
+        <is>
+          <t>O Nola funciona para restaurantes a quilo?</t>
+        </is>
+      </c>
+      <c r="D70" s="60" t="inlineStr">
+        <is>
+          <t>Sim! O Nola atende restaurantes a quilo com integração à balança de autoatendimento (add-on) e PDV adaptado para esse modelo de serviço.</t>
+        </is>
+      </c>
+      <c r="E70" s="61" t="inlineStr">
+        <is>
+          <t>quilo, self-service, peso, balança</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" s="62" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="63" t="inlineStr">
+        <is>
+          <t>hardware</t>
+        </is>
+      </c>
+      <c r="C71" s="64" t="inlineStr">
+        <is>
+          <t>Quais periféricos o Nola oferece?</t>
+        </is>
+      </c>
+      <c r="D71" s="65" t="inlineStr">
+        <is>
+          <t>Totem de Autoatendimento, Tablet de Mesa, SmartPOS (maquininha integrada), TEF (integração com maquininhas) e Balança de Autoatendimento. Todos vendidos à parte, compatíveis com os respectivos planos.</t>
+        </is>
+      </c>
+      <c r="E71" s="66" t="inlineStr">
+        <is>
+          <t>periférico, hardware, equipamento, totem, tablet, smartpos</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" s="62" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="63" t="inlineStr">
+        <is>
+          <t>hardware</t>
+        </is>
+      </c>
+      <c r="C72" s="64" t="inlineStr">
+        <is>
+          <t>O que é o SmartPOS?</t>
+        </is>
+      </c>
+      <c r="D72" s="65" t="inlineStr">
+        <is>
+          <t>SmartPOS é a maquininha de cartão integrada ao PDV do Nola. Processa pagamentos diretamente no sistema sem precisar de maquininha separada, reduzindo erros de conferência e agilizando o atendimento. Disponível a partir do plano Essencial.</t>
+        </is>
+      </c>
+      <c r="E72" s="66" t="inlineStr">
+        <is>
+          <t>smartpos, maquininha, cartão, pagamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" s="67" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="68" t="inlineStr">
+        <is>
+          <t>servicos_extra</t>
+        </is>
+      </c>
+      <c r="C73" s="69" t="inlineStr">
+        <is>
+          <t>O que é o Supfy (Marketplace de Compras)?</t>
+        </is>
+      </c>
+      <c r="D73" s="70" t="inlineStr">
+        <is>
+          <t>Supfy é o marketplace de compras integrado ao Nola onde você faz cotação automatizada com fornecedores, emite pedidos de compra e controla o CMV estratégico. Disponível como serviço add-on a partir do plano Profissional.</t>
+        </is>
+      </c>
+      <c r="E73" s="71" t="inlineStr">
+        <is>
+          <t>supfy, compras, fornecedor, cotação, marketplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" s="67" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="68" t="inlineStr">
+        <is>
+          <t>servicos_extra</t>
+        </is>
+      </c>
+      <c r="C74" s="69" t="inlineStr">
+        <is>
+          <t>O Nola tem programa de fidelidade?</t>
+        </is>
+      </c>
+      <c r="D74" s="70" t="inlineStr">
+        <is>
+          <t>Sim! O CRM + Fidelidade está disponível no plano Premium e como add-on no Profissional. Permite criar programas de pontos, cupons e campanhas para clientes recorrentes, integrado ao histórico de pedidos do PDV.</t>
+        </is>
+      </c>
+      <c r="E74" s="71" t="inlineStr">
+        <is>
+          <t>fidelidade, crm, pontos, retenção, cliente</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" s="67" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="68" t="inlineStr">
+        <is>
+          <t>servicos_extra</t>
+        </is>
+      </c>
+      <c r="C75" s="69" t="inlineStr">
+        <is>
+          <t>O Nola tem diagnóstico gratuito?</t>
+        </is>
+      </c>
+      <c r="D75" s="70" t="inlineStr">
+        <is>
+          <t>Sim! O Nola oferece Diagnóstico Estratégico gratuito e Raio-X Tributário gratuito. São serviços de avaliação que mapeiam onde seu restaurante está perdendo margem antes de qualquer compromisso de contratação.</t>
+        </is>
+      </c>
+      <c r="E75" s="71" t="inlineStr">
+        <is>
+          <t>diagnóstico, gratuito, avaliação, análise</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" s="67" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="68" t="inlineStr">
+        <is>
+          <t>servicos_extra</t>
+        </is>
+      </c>
+      <c r="C76" s="69" t="inlineStr">
+        <is>
+          <t>O Nola tem consultoria?</t>
+        </is>
+      </c>
+      <c r="D76" s="70" t="inlineStr">
+        <is>
+          <t>Sim! A Consultoria Setup 1:1 está disponível para qualquer plano. É uma consultoria personalizada para configurar o sistema conforme a realidade do seu restaurante e acelerar o retorno sobre o investimento.</t>
+        </is>
+      </c>
+      <c r="E76" s="71" t="inlineStr">
+        <is>
+          <t>consultoria, setup, 1:1, personalizado</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" s="72" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="73" t="inlineStr">
         <is>
           <t>suporte</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>Como funciona o suporte do Nola?</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>O Nola oferece suporte via nossa equipe de Customer Success com atendimento dedicado. Durante o onboarding você tem acompanhamento intensivo. Após isso, suporte contínuo para garantir que você tire o máximo do sistema.</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t>suporte, ajuda, atendimento</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="C77" s="74" t="inlineStr">
+        <is>
+          <t>Qual o horário do suporte?</t>
+        </is>
+      </c>
+      <c r="D77" s="75" t="inlineStr">
+        <is>
+          <t>Depende do plano: Essencial tem suporte via chat em horário comercial; Profissional tem suporte prioritário de segunda a sábado das 8h às 22h; Premium tem suporte 7 dias das 8h às 23h; Enterprise tem SLA de suporte garantido com gerente de conta dedicado.</t>
+        </is>
+      </c>
+      <c r="E77" s="76" t="inlineStr">
+        <is>
+          <t>suporte, horário, atendimento, chat, contato</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" s="72" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="73" t="inlineStr">
         <is>
           <t>suporte</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>Já uso outro sistema, posso migrar para o Nola?</t>
-        </is>
-      </c>
-      <c r="C18" s="15" t="inlineStr">
-        <is>
-          <t>Sim! Nossa equipe de CS te ajuda na migração com importação de cardápio, histórico e configurações. O processo é feito com suporte dedicado para não impactar sua operação.</t>
-        </is>
-      </c>
-      <c r="D18" s="15" t="inlineStr">
-        <is>
-          <t>migração, trocar sistema</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="C78" s="74" t="inlineStr">
+        <is>
+          <t>Como entro em contato com o suporte?</t>
+        </is>
+      </c>
+      <c r="D78" s="75" t="inlineStr">
+        <is>
+          <t>O suporte é feito via chat dentro do próprio sistema. Planos Premium e Enterprise têm suporte mais amplo e contato com especialistas dedicados. Para demonstração e vendas, o contato é via formulário no site (Agendar Demo).</t>
+        </is>
+      </c>
+      <c r="E78" s="76" t="inlineStr">
+        <is>
+          <t>contato, suporte, como falar, chat, telefone</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" s="72" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="73" t="inlineStr">
         <is>
           <t>suporte</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>O sistema funciona offline?</t>
-        </is>
-      </c>
-      <c r="C19" s="15" t="inlineStr">
-        <is>
-          <t>O PDV do Nola tem modo offline para não parar sua operação em caso de queda de internet. Quando a conexão volta, tudo é sincronizado automaticamente.</t>
-        </is>
-      </c>
-      <c r="D19" s="15" t="inlineStr">
-        <is>
-          <t>offline, internet, queda</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="C79" s="74" t="inlineStr">
+        <is>
+          <t>O Nola tem gerente de conta dedicado?</t>
+        </is>
+      </c>
+      <c r="D79" s="75" t="inlineStr">
+        <is>
+          <t>Sim, mas apenas no plano Enterprise. Esse gerente acompanha a operação, garante o SLA de suporte e tem acesso antecipado a novas funcionalidades.</t>
+        </is>
+      </c>
+      <c r="E79" s="76" t="inlineStr">
+        <is>
+          <t>gerente, conta, dedicado, enterprise, acompanhamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" s="77" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="78" t="inlineStr">
+        <is>
+          <t>demo_contato</t>
+        </is>
+      </c>
+      <c r="C80" s="79" t="inlineStr">
         <is>
           <t>Como agendar uma demonstração?</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>Para agendar uma demonstração gratuita do Nola, clique no botão "Agendar Demo" no topo do site. Nossa equipe entra em contato em até 24h para mostrar tudo que o sistema pode fazer pelo seu restaurante.</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>demo, demonstração, agendar, contato</t>
+      <c r="D80" s="80" t="inlineStr">
+        <is>
+          <t>Clique em 'Agendar Demo' no topo do site, preencha o formulário com seu cargo, tipo de negócio, tempo de operação e faturamento. A equipe entra em contato em até 24h para agendar a demo gratuitamente.</t>
+        </is>
+      </c>
+      <c r="E80" s="81" t="inlineStr">
+        <is>
+          <t>demo, demonstração, agendar, contato, reunião</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" s="77" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="78" t="inlineStr">
+        <is>
+          <t>demo_contato</t>
+        </is>
+      </c>
+      <c r="C81" s="79" t="inlineStr">
+        <is>
+          <t>A demonstração é gratuita?</t>
+        </is>
+      </c>
+      <c r="D81" s="80" t="inlineStr">
+        <is>
+          <t>Sim! A demonstração é 100% gratuita, sem compromisso e sem necessidade de cartão de crédito. A equipe mostra o sistema funcionando para o seu tipo de negócio especificamente.</t>
+        </is>
+      </c>
+      <c r="E81" s="81" t="inlineStr">
+        <is>
+          <t>grátis, gratuito, demo, sem compromisso</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" s="77" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="78" t="inlineStr">
+        <is>
+          <t>demo_contato</t>
+        </is>
+      </c>
+      <c r="C82" s="79" t="inlineStr">
+        <is>
+          <t>Quanto tempo dura a demonstração?</t>
+        </is>
+      </c>
+      <c r="D82" s="80" t="inlineStr">
+        <is>
+          <t>A demonstração geralmente dura entre 30 a 60 minutos, onde a equipe mostra os módulos mais relevantes para o seu negócio e responde dúvidas específicas da sua operação.</t>
+        </is>
+      </c>
+      <c r="E82" s="81" t="inlineStr">
+        <is>
+          <t>duração, tempo, quanto dura, reunião</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" s="77" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="78" t="inlineStr">
+        <is>
+          <t>demo_contato</t>
+        </is>
+      </c>
+      <c r="C83" s="79" t="inlineStr">
+        <is>
+          <t>O Nola atende toda o Brasil?</t>
+        </is>
+      </c>
+      <c r="D83" s="80" t="inlineStr">
+        <is>
+          <t>Sim! O Nola é 100% online e atende restaurantes em todo o Brasil. A implementação é remota com suporte dedicado, sem necessidade de visita presencial.</t>
+        </is>
+      </c>
+      <c r="E83" s="81" t="inlineStr">
+        <is>
+          <t>brasil, atendimento, localização, remoto, online</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D20"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="82" t="inlineStr">
+        <is>
+          <t>Categoria</t>
+        </is>
+      </c>
+      <c r="B1" s="82" t="inlineStr">
+        <is>
+          <t>Descrição</t>
+        </is>
+      </c>
+      <c r="C1" s="82" t="inlineStr"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="83" t="inlineStr">
+        <is>
+          <t>geral</t>
+        </is>
+      </c>
+      <c r="B2" s="83" t="inlineStr">
+        <is>
+          <t>Informações gerais sobre o Nola</t>
+        </is>
+      </c>
+      <c r="C2" s="83" t="inlineStr"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="84" t="inlineStr">
+        <is>
+          <t>planos</t>
+        </is>
+      </c>
+      <c r="B3" s="84" t="inlineStr">
+        <is>
+          <t>Planos, preços e o que está incluído</t>
+        </is>
+      </c>
+      <c r="C3" s="84" t="inlineStr"/>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="85" t="inlineStr">
+        <is>
+          <t>implementação</t>
+        </is>
+      </c>
+      <c r="B4" s="85" t="inlineStr">
+        <is>
+          <t>Onboarding, tempo de setup, dispositivos</t>
+        </is>
+      </c>
+      <c r="C4" s="85" t="inlineStr"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="86" t="inlineStr">
+        <is>
+          <t>integração</t>
+        </is>
+      </c>
+      <c r="B5" s="86" t="inlineStr">
+        <is>
+          <t>iFood, Rappi, pagamentos, API</t>
+        </is>
+      </c>
+      <c r="C5" s="86" t="inlineStr"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="87" t="inlineStr">
+        <is>
+          <t>pdv_operacao</t>
+        </is>
+      </c>
+      <c r="B6" s="87" t="inlineStr">
+        <is>
+          <t>PDV, KDS, mesas, cardápio digital</t>
+        </is>
+      </c>
+      <c r="C6" s="87" t="inlineStr"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="88" t="inlineStr">
+        <is>
+          <t>financeiro</t>
+        </is>
+      </c>
+      <c r="B7" s="88" t="inlineStr">
+        <is>
+          <t>DRE, fluxo de caixa, +Controle BPO</t>
+        </is>
+      </c>
+      <c r="C7" s="88" t="inlineStr"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="89" t="inlineStr">
+        <is>
+          <t>tributario</t>
+        </is>
+      </c>
+      <c r="B8" s="89" t="inlineStr">
+        <is>
+          <t>Recupera, BPO Tributário, PIS/COFINS</t>
+        </is>
+      </c>
+      <c r="C8" s="89" t="inlineStr"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="90" t="inlineStr">
+        <is>
+          <t>estoque_compras</t>
+        </is>
+      </c>
+      <c r="B9" s="90" t="inlineStr">
+        <is>
+          <t>Estoque, CMV, ficha técnica, Supfy</t>
+        </is>
+      </c>
+      <c r="C9" s="90" t="inlineStr"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="91" t="inlineStr">
+        <is>
+          <t>equipe</t>
+        </is>
+      </c>
+      <c r="B10" s="91" t="inlineStr">
+        <is>
+          <t>Guia de Gente, treinamentos, metas</t>
+        </is>
+      </c>
+      <c r="C10" s="91" t="inlineStr"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="92" t="inlineStr">
+        <is>
+          <t>inteligencia</t>
+        </is>
+      </c>
+      <c r="B11" s="92" t="inlineStr">
+        <is>
+          <t>Alertas WhatsApp, Clara IA, dashboards</t>
+        </is>
+      </c>
+      <c r="C11" s="92" t="inlineStr"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="93" t="inlineStr">
+        <is>
+          <t>franquias</t>
+        </is>
+      </c>
+      <c r="B12" s="93" t="inlineStr">
+        <is>
+          <t>Multi-unidade, dashboard consolidado</t>
+        </is>
+      </c>
+      <c r="C12" s="93" t="inlineStr"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="94" t="inlineStr">
+        <is>
+          <t>tipos_negocio</t>
+        </is>
+      </c>
+      <c r="B13" s="94" t="inlineStr">
+        <is>
+          <t>Pizzaria, hamburgueria, dark kitchen, etc</t>
+        </is>
+      </c>
+      <c r="C13" s="94" t="inlineStr"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="95" t="inlineStr">
+        <is>
+          <t>hardware</t>
+        </is>
+      </c>
+      <c r="B14" s="95" t="inlineStr">
+        <is>
+          <t>Periféricos: SmartPOS, totem, tablet</t>
+        </is>
+      </c>
+      <c r="C14" s="95" t="inlineStr"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="96" t="inlineStr">
+        <is>
+          <t>servicos_extra</t>
+        </is>
+      </c>
+      <c r="B15" s="96" t="inlineStr">
+        <is>
+          <t>Supfy, CRM Fidelidade, Diagnóstico</t>
+        </is>
+      </c>
+      <c r="C15" s="96" t="inlineStr"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="97" t="inlineStr">
+        <is>
+          <t>suporte</t>
+        </is>
+      </c>
+      <c r="B16" s="97" t="inlineStr">
+        <is>
+          <t>Horários, canais, gerente de conta</t>
+        </is>
+      </c>
+      <c r="C16" s="97" t="inlineStr"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="98" t="inlineStr">
+        <is>
+          <t>demo_contato</t>
+        </is>
+      </c>
+      <c r="B17" s="98" t="inlineStr">
+        <is>
+          <t>Como agendar demo, contato, Brasil</t>
+        </is>
+      </c>
+      <c r="C17" s="98" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/nola_knowledge_base.xlsx
+++ b/nola_knowledge_base.xlsx
@@ -839,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E83"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2923,6 +2923,405 @@
       <c r="E83" s="81" t="inlineStr">
         <is>
           <t>brasil, atendimento, localização, remoto, online</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ecossistema</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Quais sao os modulos do ecossistema Nola?</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>O ecossistema Nola tem 6 modulos integrados:
+Operacao &amp; PDV - PDV em nuvem, mesas, delivery e KDS
+Financeiro - DRE automatico, fluxo de caixa e conciliacao OFX
+Tributario - BPO tributario e recuperacao de margem (Recupera)
+Compras &amp; Estoque - Ficha tecnica, CMV real e contagem cega (Supfy)
+Gestao de Equipe - Treinamentos, checklists com foto e metas gamificadas (Guia de Gente)
+Inteligencia - Alertas WhatsApp, dashboards e relatorios automaticos
+Tudo em uma unica plataforma integrada. Investimento a partir de R$450/mes. ecossistema</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>ecossistema, modulos, tudo, completo, o que tem, sistema completo, 6 modulos</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ecossistema</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Me explica o ecossistema do Nola</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>O Nola e um ecossistema 360 para restaurantes com 6 modulos integrados:
+Operacao &amp; PDV: PDV em nuvem, mesas, balcao, delivery e KDS por praca
+Financeiro: DRE automatico todo mes, fluxo de caixa D+1 e conciliacao bancaria via OFX
+Tributario: Recuperacao de impostos pagos a mais via BPO Tributario (Recupera)
+Compras &amp; Estoque: CMV real, ficha tecnica cascata e contagem cega anti-fraude (Supfy)
+Gestao de Equipe: Guia de Gente com treinamentos em video, checklists e canal anonimo
+Inteligencia: Funcionario Dedo-Duro - alertas de desvios em tempo real no WhatsApp
+Quer conhecer tudo? ecossistema</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>ecossistema, modulos, funcionalidades, completo, explicar, como funciona</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>dor_cmv</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Meu CMV esta muito alto, o que faco?</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>CMV alto e um dos problemas mais silenciosos do restaurante — voce perde margem sem perceber.
+O Nola foi criado por quem viveu essa dor e resolve de ponta a ponta:
+- Ficha tecnica com baixa automatica do insumo ao prato final
+- Contagem cega no celular: operador conta sem ver o estoque, zero fraude
+- Alerta automatico quando o CMV sai da meta definida
+Media entre os clientes: -35% de desperdicio e custo real de cada prato na palma da mao. resolver cmv</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>cmv alto, custo alto, desperdicio, food cost, custo mercadoria, margem baixa, estoque</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>dor_cmv</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Nao sei quanto custa cada prato do cardapio</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Vender sem saber o custo de cada prato e como dirigir no escuro. Voce pode estar perdendo margem em todo pedido.
+O Nola resolve isso com ficha tecnica em cascata: voce cadastra os ingredientes uma vez e o sistema calcula automaticamente o custo de cada prato, sub-receita e combo.
+Resultado: visibilidade total de margem por produto, sem planilha, sem chute. resolver cmv</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>custo prato, preco cardapio, quanto custa, ficha tecnica, precificacao, margem por prato</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>dor_cmv</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Tenho muito desperdicio no estoque</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Desperdicio invisivel corroi a margem todo mes — e quase sempre e fraude ou ficha tecnica errada.
+O Nola combate os dois com contagem cega no celular (operador conta sem ver o sistema) e baixa automatica por ficha tecnica. Qualquer desvio entre o teorico e o real dispara alerta.
+Media de -35% de desperdicio nos primeiros meses. resolver cmv</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>desperdicio, perda, estoque, cmv, insumo, ingrediente</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>dor_financeiro</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Meu financeiro esta uma baguncas</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Financeiro baguncado quase sempre vem do mesmo trio: DRE feito em planilha, sempre atrasado, nunca confiavel.
+O Nola automatiza tudo isso:
+- DRE gerado todo mes com base nas vendas e despesas reais do sistema
+- Fluxo de caixa D+1: voce sabe hoje o que entra e sai amanha
+- Conciliacao bancaria via OFX automatica, sem relancamento manual
+Zero planilhas. -90% de tempo em conciliacao. DRE 100% confiavel. resolver financeiro</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>financeiro baguncado, dre, fluxo de caixa, planilha, conciliacao, baguncas, desorganizado</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>dor_financeiro</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Nao sei se meu restaurante esta dando lucro</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Se voce nao tem um DRE confiavel, e impossivel saber — e esse e um dos problemas mais comuns.
+O Nola gera o DRE automaticamente todo mes com base nos dados reais do sistema. Voce ve exatamente onde ganha, onde perde e quanto sobra — sem depender de contador pra montar. resolver financeiro</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>lucro, prejuizo, dre, resultado, saber se lucra, financeiro, margem, resultado mensal</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>dor_financeiro</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Tenho problema com fluxo de caixa</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Fluxo desorganizado gera surpresas no fim do mes — e quase sempre e falta de visibilidade, nao de dinheiro.
+O Nola traz visibilidade real: fluxo D+1 (voce sabe hoje o que entra e sai amanha), separando regime caixa de competencia. Conciliacao via OFX elimina divergencias silenciosas. resolver financeiro</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>fluxo de caixa, dinheiro, caixa, previsao, entrada, saida, conciliacao</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>dor_equipe</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Minha equipe nao tem padrao</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Equipe sem padrao e dono preso na operacao — voce nao consegue sair sem tudo parar.
+O Nola tem o Guia de Gente, modulo de equipe criado exatamente pra isso:
+- Treinamentos em video por funcao com prova obrigatoria (minimo 80% para passar)
+- Checklists diarios com foto como evidencia real
+- Canal anonimo para funcionario reportar problemas sem medo
+- Metas gamificadas com ranking em tempo real no PDV
+Resultado: -40% de turnover e o dono consegue monitorar tudo pelo celular de qualquer lugar. resolver equipe</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>equipe sem padrao, funcionarios, treinamento, turnover, checklists, padronizacao, guia de gente</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>dor_equipe</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Tenho muito turnover na equipe</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Turnover alto custa caro e prende o dono na operacao — cada saida e horas de retreinamento perdidas.
+O Nola tem o Guia de Gente para resolver isso:
+- Onboarding estruturado com trilha de treinamento por funcao
+- Canal anonimo onde o funcionario fala antes de pedir demissao
+- Checklists e metas que criam rotina e engajamento
+Media de -40% de turnover entre os clientes que usam o modulo. resolver equipe</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>turnover, rotatividade, demissao, contratar, perder funcionario</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>dor_equipe</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Nao consigo me afastar do restaurante</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Se o restaurante para quando voce sai, e sinal de que falta processo, nao pessoa.
+O Nola resolve isso com padronizacao real: treinamentos em video, checklists com foto e o Funcionario Dedo-Duro que avisa no seu WhatsApp se algo sair do padrao — mesmo voce estando fora. resolver equipe</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>afastar, presenca, depende de mim, gestao remota, monitorar longe, dono preso</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>dor_integracao</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Uso varios sistemas que nao se integram</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Ter 3 ou 4 sistemas separados e um dos maiores geradores de retrabalho em restaurante. Voce lanca o mesmo dado multiplas vezes e ainda assim os numeros nao batem.
+O Nola substitui tudo com um unico ecossistema integrado:
+- PDV, financeiro, estoque, equipe e inteligencia em uma plataforma so
+- Dados de venda alimentam automaticamente financeiro, estoque e alertas
+- Multi-delivery (iFood, Rappi, Uber Eats) em uma tela unica
+Um sistema substitui 4+. -70% de retrabalho em lancamento de dados. resolver integracao</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>varios sistemas, nao integra, sistemas separados, retrabalho, dados duplicados, integracao</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>dor_integracao</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Meus dados nao conversam entre os sistemas</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Sistemas que nao conversam geram divergencias silenciosas — voce so descobre o erro no fim do mes.
+O Nola integra tudo nativamente: os dados de venda alimentam o financeiro, o estoque e os alertas em tempo real, sem precisar relancar nada em outro sistema. Zero divergencia, zero retrabalho. resolver integracao</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>dados, integracao, sistema, divergencia, relancar, duplo lancamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>dor_integracao</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Quero um sistema unico para o restaurante</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>O Nola foi criado exatamente por donos de restaurante que sofreram com sistemas fragmentados.
+Um unico ecossistema integrado: PDV, financeiro, estoque, equipe e inteligencia — tudo conectado, com multi-delivery (iFood, Rappi, Uber Eats) em uma tela so. ecossistema</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>sistema unico, tudo em um, unificado, integrado, solucao completa, ecossistema</t>
         </is>
       </c>
     </row>
